--- a/Data/EXCEL/Transfer/salemon/202512/6549-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/6549-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{332AC428-B5AC-43A8-9335-4B8223484963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0CE5CED-7D6C-428F-9EAD-73B4DC6093FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{16C152CC-3926-4A85-A847-64EA461A236B}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{7E2065F7-FF31-4262-B6F3-E147307DA20C}"/>
   </bookViews>
   <sheets>
     <sheet name="6549-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -860,10 +860,10 @@
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,21 +1258,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6C5967-AC80-4A45-B764-D4DCA7280269}">
-  <dimension ref="A1:Q43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2035121-AA99-4725-9778-2B768E2DD0E5}">
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="14.375" customWidth="1"/>
-    <col min="8" max="8" width="12.625" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="12.625" customWidth="1"/>
-    <col min="14" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="12.625" customWidth="1"/>
-    <col min="17" max="17" width="12.5" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="6" width="7.875" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="7.875" customWidth="1"/>
+    <col min="9" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="13" width="7.875" customWidth="1"/>
+    <col min="14" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="7.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1425,25 +1425,25 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>7.85</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="C5" s="6">
-        <v>8.0299999999999994</v>
+        <v>7.71</v>
       </c>
       <c r="D5" s="6">
-        <v>9.5299999999999994</v>
+        <v>8.01</v>
       </c>
       <c r="E5" s="6">
-        <v>7.5</v>
+        <v>7.51</v>
       </c>
       <c r="F5" s="7">
-        <v>0.18</v>
+        <v>-0.32</v>
       </c>
       <c r="G5" s="7">
-        <v>2.29</v>
+        <v>-3.99</v>
       </c>
       <c r="H5" s="8">
         <v>0</v>
@@ -1478,25 +1478,25 @@
     </row>
     <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="11">
+        <v>7.85</v>
+      </c>
+      <c r="C6" s="11">
         <v>8.0299999999999994</v>
       </c>
-      <c r="C6" s="11">
-        <v>7.85</v>
-      </c>
       <c r="D6" s="11">
-        <v>8.15</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="E6" s="11">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="F6" s="12">
-        <v>-0.18</v>
+        <v>0.18</v>
       </c>
       <c r="G6" s="12">
-        <v>-2.2400000000000002</v>
+        <v>2.29</v>
       </c>
       <c r="H6" s="13">
         <v>0</v>
@@ -1531,25 +1531,25 @@
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>7.8</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="C7" s="6">
-        <v>8.0299999999999994</v>
+        <v>7.85</v>
       </c>
       <c r="D7" s="6">
-        <v>10.6</v>
+        <v>8.15</v>
       </c>
       <c r="E7" s="6">
-        <v>7.22</v>
+        <v>7.7</v>
       </c>
       <c r="F7" s="7">
-        <v>0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="G7" s="7">
-        <v>2.95</v>
+        <v>-2.2400000000000002</v>
       </c>
       <c r="H7" s="8">
         <v>0</v>
@@ -1584,25 +1584,25 @@
     </row>
     <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="11">
-        <v>7.88</v>
+        <v>7.8</v>
       </c>
       <c r="C8" s="11">
-        <v>7.8</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="D8" s="11">
-        <v>8.57</v>
+        <v>10.6</v>
       </c>
       <c r="E8" s="11">
-        <v>7.41</v>
+        <v>7.22</v>
       </c>
       <c r="F8" s="12">
-        <v>-0.08</v>
+        <v>0.23</v>
       </c>
       <c r="G8" s="12">
-        <v>-1.02</v>
+        <v>2.95</v>
       </c>
       <c r="H8" s="13">
         <v>0</v>
@@ -1637,25 +1637,25 @@
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
+        <v>7.88</v>
+      </c>
+      <c r="C9" s="6">
         <v>7.8</v>
       </c>
-      <c r="C9" s="6">
-        <v>7.88</v>
-      </c>
       <c r="D9" s="6">
-        <v>8.27</v>
+        <v>8.57</v>
       </c>
       <c r="E9" s="6">
-        <v>7.57</v>
+        <v>7.41</v>
       </c>
       <c r="F9" s="7">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="G9" s="7">
-        <v>1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="H9" s="8">
         <v>0</v>
@@ -1690,25 +1690,25 @@
     </row>
     <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="11">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="C10" s="11">
-        <v>7.8</v>
+        <v>7.88</v>
       </c>
       <c r="D10" s="11">
-        <v>9.9</v>
+        <v>8.27</v>
       </c>
       <c r="E10" s="11">
-        <v>7.53</v>
-      </c>
-      <c r="F10" s="14">
-        <v>0.01</v>
-      </c>
-      <c r="G10" s="14">
-        <v>0.13</v>
+        <v>7.57</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="G10" s="12">
+        <v>1.03</v>
       </c>
       <c r="H10" s="13">
         <v>0</v>
@@ -1743,25 +1743,25 @@
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>8</v>
+        <v>7.79</v>
       </c>
       <c r="C11" s="6">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="D11" s="6">
-        <v>8.0399999999999991</v>
+        <v>9.9</v>
       </c>
       <c r="E11" s="6">
-        <v>7.45</v>
-      </c>
-      <c r="F11" s="15">
-        <v>-0.21</v>
-      </c>
-      <c r="G11" s="15">
-        <v>-2.62</v>
+        <v>7.53</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0.01</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0.13</v>
       </c>
       <c r="H11" s="8">
         <v>0</v>
@@ -1796,25 +1796,25 @@
     </row>
     <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="11">
-        <v>8</v>
+        <v>7.79</v>
       </c>
       <c r="D12" s="11">
-        <v>9.0500000000000007</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="E12" s="11">
-        <v>6.99</v>
-      </c>
-      <c r="F12" s="12">
-        <v>-1</v>
-      </c>
-      <c r="G12" s="12">
-        <v>-11.11</v>
+        <v>7.45</v>
+      </c>
+      <c r="F12" s="15">
+        <v>-0.21</v>
+      </c>
+      <c r="G12" s="15">
+        <v>-2.62</v>
       </c>
       <c r="H12" s="13">
         <v>0</v>
@@ -1849,25 +1849,25 @@
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6">
-        <v>8.9700000000000006</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="6">
-        <v>9.7799999999999994</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="E13" s="6">
-        <v>8.68</v>
+        <v>6.99</v>
       </c>
       <c r="F13" s="7">
-        <v>0.03</v>
+        <v>-1</v>
       </c>
       <c r="G13" s="7">
-        <v>0.33</v>
+        <v>-11.11</v>
       </c>
       <c r="H13" s="8">
         <v>0</v>
@@ -1902,25 +1902,25 @@
     </row>
     <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="11">
-        <v>8.5</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="C14" s="11">
-        <v>8.9700000000000006</v>
+        <v>9</v>
       </c>
       <c r="D14" s="11">
-        <v>9.4700000000000006</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="E14" s="11">
-        <v>8.16</v>
-      </c>
-      <c r="F14" s="14">
-        <v>0.47</v>
-      </c>
-      <c r="G14" s="14">
-        <v>5.53</v>
+        <v>8.68</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0.33</v>
       </c>
       <c r="H14" s="13">
         <v>0</v>
@@ -1955,25 +1955,25 @@
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6">
-        <v>8.1999999999999993</v>
+        <v>8.5</v>
       </c>
       <c r="C15" s="6">
-        <v>8.5</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="D15" s="6">
-        <v>9.0299999999999994</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="E15" s="6">
-        <v>7.7</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="G15" s="7">
-        <v>3.66</v>
+        <v>8.16</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5.53</v>
       </c>
       <c r="H15" s="8">
         <v>0</v>
@@ -2008,25 +2008,25 @@
     </row>
     <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="11">
-        <v>8.93</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="C16" s="11">
-        <v>8.1999999999999993</v>
+        <v>8.5</v>
       </c>
       <c r="D16" s="11">
-        <v>9.69</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="E16" s="11">
-        <v>7.63</v>
+        <v>7.7</v>
       </c>
       <c r="F16" s="12">
-        <v>-0.73</v>
+        <v>0.3</v>
       </c>
       <c r="G16" s="12">
-        <v>-8.17</v>
+        <v>3.66</v>
       </c>
       <c r="H16" s="13">
         <v>0</v>
@@ -2040,8 +2040,8 @@
       <c r="K16" s="13">
         <v>0</v>
       </c>
-      <c r="L16" s="12">
-        <v>-100</v>
+      <c r="L16" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="M16" s="13">
         <v>0</v>
@@ -2055,31 +2055,31 @@
       <c r="P16" s="13">
         <v>0</v>
       </c>
-      <c r="Q16" s="12">
-        <v>-100</v>
+      <c r="Q16" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B17" s="6">
-        <v>10</v>
+        <v>8.93</v>
       </c>
       <c r="C17" s="6">
-        <v>8.93</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="D17" s="6">
-        <v>10.050000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="E17" s="6">
-        <v>8.84</v>
-      </c>
-      <c r="F17" s="15">
-        <v>-1.07</v>
-      </c>
-      <c r="G17" s="15">
-        <v>-10.7</v>
+        <v>7.63</v>
+      </c>
+      <c r="F17" s="7">
+        <v>-0.73</v>
+      </c>
+      <c r="G17" s="7">
+        <v>-8.17</v>
       </c>
       <c r="H17" s="8">
         <v>0</v>
@@ -2093,7 +2093,7 @@
       <c r="K17" s="8">
         <v>0</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="7">
         <v>-100</v>
       </c>
       <c r="M17" s="8">
@@ -2108,31 +2108,31 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="7">
         <v>-100</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B18" s="11">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="C18" s="11">
-        <v>10</v>
+        <v>8.93</v>
       </c>
       <c r="D18" s="11">
-        <v>10.65</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="E18" s="11">
-        <v>9.67</v>
-      </c>
-      <c r="F18" s="12">
-        <v>-0.15</v>
-      </c>
-      <c r="G18" s="12">
-        <v>-1.48</v>
+        <v>8.84</v>
+      </c>
+      <c r="F18" s="15">
+        <v>-1.07</v>
+      </c>
+      <c r="G18" s="15">
+        <v>-10.7</v>
       </c>
       <c r="H18" s="13">
         <v>0</v>
@@ -2146,7 +2146,7 @@
       <c r="K18" s="13">
         <v>0</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="15">
         <v>-100</v>
       </c>
       <c r="M18" s="13">
@@ -2161,31 +2161,31 @@
       <c r="P18" s="13">
         <v>0</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="6">
-        <v>10.6</v>
+        <v>10.15</v>
       </c>
       <c r="C19" s="6">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="D19" s="6">
-        <v>10.6</v>
+        <v>10.65</v>
       </c>
       <c r="E19" s="6">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="F19" s="15">
-        <v>-0.45</v>
-      </c>
-      <c r="G19" s="15">
-        <v>-4.25</v>
+        <v>9.67</v>
+      </c>
+      <c r="F19" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="G19" s="7">
+        <v>-1.48</v>
       </c>
       <c r="H19" s="8">
         <v>0</v>
@@ -2199,7 +2199,7 @@
       <c r="K19" s="8">
         <v>0</v>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="7">
         <v>-100</v>
       </c>
       <c r="M19" s="8">
@@ -2214,31 +2214,31 @@
       <c r="P19" s="8">
         <v>0</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="7">
         <v>-100</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="11">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="C20" s="11">
+        <v>10.15</v>
+      </c>
+      <c r="D20" s="11">
         <v>10.6</v>
       </c>
-      <c r="D20" s="11">
-        <v>11.85</v>
-      </c>
       <c r="E20" s="11">
-        <v>9.6</v>
-      </c>
-      <c r="F20" s="12">
-        <v>-0.65</v>
-      </c>
-      <c r="G20" s="12">
-        <v>-5.78</v>
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F20" s="15">
+        <v>-0.45</v>
+      </c>
+      <c r="G20" s="15">
+        <v>-4.25</v>
       </c>
       <c r="H20" s="13">
         <v>0</v>
@@ -2252,7 +2252,7 @@
       <c r="K20" s="13">
         <v>0</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="15">
         <v>-100</v>
       </c>
       <c r="M20" s="13">
@@ -2267,31 +2267,31 @@
       <c r="P20" s="13">
         <v>0</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="Q20" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="6">
-        <v>11.95</v>
+        <v>11.25</v>
       </c>
       <c r="C21" s="6">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="D21" s="6">
-        <v>13</v>
+        <v>11.85</v>
       </c>
       <c r="E21" s="6">
-        <v>10.95</v>
-      </c>
-      <c r="F21" s="15">
-        <v>-0.7</v>
-      </c>
-      <c r="G21" s="15">
-        <v>-5.86</v>
+        <v>9.6</v>
+      </c>
+      <c r="F21" s="7">
+        <v>-0.65</v>
+      </c>
+      <c r="G21" s="7">
+        <v>-5.78</v>
       </c>
       <c r="H21" s="8">
         <v>0</v>
@@ -2305,7 +2305,7 @@
       <c r="K21" s="8">
         <v>0</v>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="7">
         <v>-100</v>
       </c>
       <c r="M21" s="8">
@@ -2320,31 +2320,31 @@
       <c r="P21" s="8">
         <v>0</v>
       </c>
-      <c r="Q21" s="15">
+      <c r="Q21" s="7">
         <v>-100</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B22" s="11">
-        <v>11.8</v>
+        <v>11.95</v>
       </c>
       <c r="C22" s="11">
-        <v>11.95</v>
+        <v>11.25</v>
       </c>
       <c r="D22" s="11">
-        <v>12.55</v>
+        <v>13</v>
       </c>
       <c r="E22" s="11">
-        <v>10.75</v>
-      </c>
-      <c r="F22" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1.27</v>
+        <v>10.95</v>
+      </c>
+      <c r="F22" s="15">
+        <v>-0.7</v>
+      </c>
+      <c r="G22" s="15">
+        <v>-5.86</v>
       </c>
       <c r="H22" s="13">
         <v>0</v>
@@ -2358,7 +2358,7 @@
       <c r="K22" s="13">
         <v>0</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="15">
         <v>-100</v>
       </c>
       <c r="M22" s="13">
@@ -2373,31 +2373,31 @@
       <c r="P22" s="13">
         <v>0</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="6">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="C23" s="6">
-        <v>11.8</v>
+        <v>11.95</v>
       </c>
       <c r="D23" s="6">
-        <v>13.2</v>
+        <v>12.55</v>
       </c>
       <c r="E23" s="6">
-        <v>11.45</v>
-      </c>
-      <c r="F23" s="15">
-        <v>-1.4</v>
-      </c>
-      <c r="G23" s="15">
-        <v>-10.61</v>
+        <v>10.75</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1.27</v>
       </c>
       <c r="H23" s="8">
         <v>0</v>
@@ -2411,7 +2411,7 @@
       <c r="K23" s="8">
         <v>0</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="7">
         <v>-100</v>
       </c>
       <c r="M23" s="8">
@@ -2426,31 +2426,31 @@
       <c r="P23" s="8">
         <v>0</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="7">
         <v>-100</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="11">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="C24" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="D24" s="11">
         <v>13.2</v>
       </c>
-      <c r="D24" s="11">
-        <v>14.05</v>
-      </c>
       <c r="E24" s="11">
-        <v>11.5</v>
-      </c>
-      <c r="F24" s="12">
-        <v>-0.5</v>
-      </c>
-      <c r="G24" s="12">
-        <v>-3.65</v>
+        <v>11.45</v>
+      </c>
+      <c r="F24" s="15">
+        <v>-1.4</v>
+      </c>
+      <c r="G24" s="15">
+        <v>-10.61</v>
       </c>
       <c r="H24" s="13">
         <v>0</v>
@@ -2464,7 +2464,7 @@
       <c r="K24" s="13">
         <v>0</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="15">
         <v>-100</v>
       </c>
       <c r="M24" s="13">
@@ -2479,31 +2479,31 @@
       <c r="P24" s="13">
         <v>0</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="6">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="C25" s="6">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="D25" s="6">
-        <v>14.85</v>
+        <v>14.05</v>
       </c>
       <c r="E25" s="6">
-        <v>13.05</v>
-      </c>
-      <c r="F25" s="15">
-        <v>-0.2</v>
-      </c>
-      <c r="G25" s="15">
-        <v>-1.44</v>
+        <v>11.5</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="G25" s="7">
+        <v>-3.65</v>
       </c>
       <c r="H25" s="8">
         <v>0</v>
@@ -2517,7 +2517,7 @@
       <c r="K25" s="8">
         <v>0</v>
       </c>
-      <c r="L25" s="15">
+      <c r="L25" s="7">
         <v>-100</v>
       </c>
       <c r="M25" s="8">
@@ -2532,31 +2532,31 @@
       <c r="P25" s="8">
         <v>0</v>
       </c>
-      <c r="Q25" s="15">
+      <c r="Q25" s="7">
         <v>-100</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="11">
-        <v>14.05</v>
+        <v>13.9</v>
       </c>
       <c r="C26" s="11">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="D26" s="11">
-        <v>15.05</v>
+        <v>14.85</v>
       </c>
       <c r="E26" s="11">
-        <v>13.45</v>
-      </c>
-      <c r="F26" s="12">
-        <v>-0.15</v>
-      </c>
-      <c r="G26" s="12">
-        <v>-1.07</v>
+        <v>13.05</v>
+      </c>
+      <c r="F26" s="15">
+        <v>-0.2</v>
+      </c>
+      <c r="G26" s="15">
+        <v>-1.44</v>
       </c>
       <c r="H26" s="13">
         <v>0</v>
@@ -2570,7 +2570,7 @@
       <c r="K26" s="13">
         <v>0</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="15">
         <v>-100</v>
       </c>
       <c r="M26" s="13">
@@ -2585,31 +2585,31 @@
       <c r="P26" s="13">
         <v>0</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="Q26" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="6">
-        <v>14.75</v>
+        <v>14.05</v>
       </c>
       <c r="C27" s="6">
-        <v>14.05</v>
+        <v>13.9</v>
       </c>
       <c r="D27" s="6">
-        <v>16.600000000000001</v>
+        <v>15.05</v>
       </c>
       <c r="E27" s="6">
-        <v>13.55</v>
-      </c>
-      <c r="F27" s="15">
-        <v>-0.7</v>
-      </c>
-      <c r="G27" s="15">
-        <v>-4.75</v>
+        <v>13.45</v>
+      </c>
+      <c r="F27" s="7">
+        <v>-0.15</v>
+      </c>
+      <c r="G27" s="7">
+        <v>-1.07</v>
       </c>
       <c r="H27" s="8">
         <v>0</v>
@@ -2617,13 +2617,13 @@
       <c r="I27" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="15">
-        <v>-100</v>
+      <c r="J27" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="K27" s="8">
         <v>0</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="7">
         <v>-100</v>
       </c>
       <c r="M27" s="8">
@@ -2632,37 +2632,37 @@
       <c r="N27" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O27" s="15">
-        <v>-100</v>
+      <c r="O27" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="P27" s="8">
         <v>0</v>
       </c>
-      <c r="Q27" s="15">
+      <c r="Q27" s="7">
         <v>-100</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="11">
-        <v>16.399999999999999</v>
+        <v>14.75</v>
       </c>
       <c r="C28" s="11">
-        <v>14.75</v>
+        <v>14.05</v>
       </c>
       <c r="D28" s="11">
-        <v>17.05</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E28" s="11">
-        <v>14.4</v>
-      </c>
-      <c r="F28" s="12">
-        <v>-1.65</v>
-      </c>
-      <c r="G28" s="12">
-        <v>-10.06</v>
+        <v>13.55</v>
+      </c>
+      <c r="F28" s="15">
+        <v>-0.7</v>
+      </c>
+      <c r="G28" s="15">
+        <v>-4.75</v>
       </c>
       <c r="H28" s="13">
         <v>0</v>
@@ -2670,14 +2670,14 @@
       <c r="I28" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="15">
         <v>-100</v>
       </c>
       <c r="K28" s="13">
-        <v>0.22700000000000001</v>
-      </c>
-      <c r="L28" s="14">
-        <v>48.1</v>
+        <v>0</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-100</v>
       </c>
       <c r="M28" s="13">
         <v>0</v>
@@ -2685,37 +2685,37 @@
       <c r="N28" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O28" s="12">
+      <c r="O28" s="15">
         <v>-100</v>
       </c>
       <c r="P28" s="13">
-        <v>0.22700000000000001</v>
-      </c>
-      <c r="Q28" s="14">
-        <v>48.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" s="6">
-        <v>13.65</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="C29" s="6">
-        <v>16.399999999999999</v>
+        <v>14.75</v>
       </c>
       <c r="D29" s="6">
-        <v>19.100000000000001</v>
+        <v>17.05</v>
       </c>
       <c r="E29" s="6">
-        <v>12.55</v>
+        <v>14.4</v>
       </c>
       <c r="F29" s="7">
-        <v>2.75</v>
+        <v>-1.65</v>
       </c>
       <c r="G29" s="7">
-        <v>20.149999999999999</v>
+        <v>-10.06</v>
       </c>
       <c r="H29" s="8">
         <v>0</v>
@@ -2723,14 +2723,14 @@
       <c r="I29" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="8" t="s">
-        <v>17</v>
+      <c r="J29" s="7">
+        <v>-100</v>
       </c>
       <c r="K29" s="8">
         <v>0.22700000000000001</v>
       </c>
-      <c r="L29" s="8" t="s">
-        <v>17</v>
+      <c r="L29" s="14">
+        <v>48.1</v>
       </c>
       <c r="M29" s="8">
         <v>0</v>
@@ -2738,37 +2738,37 @@
       <c r="N29" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O29" s="8" t="s">
-        <v>17</v>
+      <c r="O29" s="7">
+        <v>-100</v>
       </c>
       <c r="P29" s="8">
         <v>0.22700000000000001</v>
       </c>
-      <c r="Q29" s="8" t="s">
-        <v>17</v>
+      <c r="Q29" s="14">
+        <v>48.1</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B30" s="11">
-        <v>15</v>
+        <v>13.65</v>
       </c>
       <c r="C30" s="11">
-        <v>13.65</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D30" s="11">
-        <v>15.3</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="E30" s="11">
-        <v>13.35</v>
+        <v>12.55</v>
       </c>
       <c r="F30" s="12">
-        <v>-1.35</v>
+        <v>2.75</v>
       </c>
       <c r="G30" s="12">
-        <v>-9</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="H30" s="13">
         <v>0</v>
@@ -2803,25 +2803,25 @@
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="6">
-        <v>15.05</v>
+        <v>15</v>
       </c>
       <c r="C31" s="6">
-        <v>15</v>
+        <v>13.65</v>
       </c>
       <c r="D31" s="6">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="E31" s="6">
-        <v>14.3</v>
-      </c>
-      <c r="F31" s="15">
-        <v>-0.05</v>
-      </c>
-      <c r="G31" s="15">
-        <v>-0.33</v>
+        <v>13.35</v>
+      </c>
+      <c r="F31" s="7">
+        <v>-1.35</v>
+      </c>
+      <c r="G31" s="7">
+        <v>-9</v>
       </c>
       <c r="H31" s="8">
         <v>0</v>
@@ -2856,25 +2856,25 @@
     </row>
     <row r="32" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B32" s="11">
-        <v>17.850000000000001</v>
+        <v>15.05</v>
       </c>
       <c r="C32" s="11">
-        <v>15.05</v>
+        <v>15</v>
       </c>
       <c r="D32" s="11">
-        <v>19.2</v>
+        <v>16.2</v>
       </c>
       <c r="E32" s="11">
-        <v>13.55</v>
-      </c>
-      <c r="F32" s="12">
-        <v>-2.8</v>
-      </c>
-      <c r="G32" s="12">
-        <v>-15.69</v>
+        <v>14.3</v>
+      </c>
+      <c r="F32" s="15">
+        <v>-0.05</v>
+      </c>
+      <c r="G32" s="15">
+        <v>-0.33</v>
       </c>
       <c r="H32" s="13">
         <v>0</v>
@@ -2909,25 +2909,25 @@
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B33" s="6">
-        <v>24.65</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="C33" s="6">
-        <v>17.850000000000001</v>
+        <v>15.05</v>
       </c>
       <c r="D33" s="6">
-        <v>27</v>
+        <v>19.2</v>
       </c>
       <c r="E33" s="6">
-        <v>16.45</v>
-      </c>
-      <c r="F33" s="15">
-        <v>-6.8</v>
-      </c>
-      <c r="G33" s="15">
-        <v>-27.59</v>
+        <v>13.55</v>
+      </c>
+      <c r="F33" s="7">
+        <v>-2.8</v>
+      </c>
+      <c r="G33" s="7">
+        <v>-15.69</v>
       </c>
       <c r="H33" s="8">
         <v>0</v>
@@ -2962,25 +2962,25 @@
     </row>
     <row r="34" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B34" s="11">
-        <v>28.95</v>
+        <v>24.65</v>
       </c>
       <c r="C34" s="11">
-        <v>24.65</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="D34" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>23.95</v>
-      </c>
-      <c r="F34" s="12">
-        <v>-4.3</v>
-      </c>
-      <c r="G34" s="12">
-        <v>-14.85</v>
+        <v>16.45</v>
+      </c>
+      <c r="F34" s="15">
+        <v>-6.8</v>
+      </c>
+      <c r="G34" s="15">
+        <v>-27.59</v>
       </c>
       <c r="H34" s="13">
         <v>0</v>
@@ -3015,25 +3015,25 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B35" s="6">
-        <v>29.25</v>
+        <v>28.95</v>
       </c>
       <c r="C35" s="6">
-        <v>28.95</v>
+        <v>24.65</v>
       </c>
       <c r="D35" s="6">
-        <v>30.9</v>
+        <v>30</v>
       </c>
       <c r="E35" s="6">
-        <v>22.25</v>
-      </c>
-      <c r="F35" s="15">
-        <v>-0.3</v>
-      </c>
-      <c r="G35" s="15">
-        <v>-1.03</v>
+        <v>23.95</v>
+      </c>
+      <c r="F35" s="7">
+        <v>-4.3</v>
+      </c>
+      <c r="G35" s="7">
+        <v>-14.85</v>
       </c>
       <c r="H35" s="8">
         <v>0</v>
@@ -3068,25 +3068,25 @@
     </row>
     <row r="36" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B36" s="11">
-        <v>32.950000000000003</v>
+        <v>29.25</v>
       </c>
       <c r="C36" s="11">
-        <v>29.25</v>
+        <v>28.95</v>
       </c>
       <c r="D36" s="11">
-        <v>33.5</v>
+        <v>30.9</v>
       </c>
       <c r="E36" s="11">
-        <v>27.35</v>
-      </c>
-      <c r="F36" s="12">
-        <v>-3.7</v>
-      </c>
-      <c r="G36" s="12">
-        <v>-11.23</v>
+        <v>22.25</v>
+      </c>
+      <c r="F36" s="15">
+        <v>-0.3</v>
+      </c>
+      <c r="G36" s="15">
+        <v>-1.03</v>
       </c>
       <c r="H36" s="13">
         <v>0</v>
@@ -3121,25 +3121,25 @@
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B37" s="6">
-        <v>40.25</v>
+        <v>32.950000000000003</v>
       </c>
       <c r="C37" s="6">
-        <v>32.950000000000003</v>
+        <v>29.25</v>
       </c>
       <c r="D37" s="6">
-        <v>41.55</v>
+        <v>33.5</v>
       </c>
       <c r="E37" s="6">
-        <v>28.55</v>
-      </c>
-      <c r="F37" s="15">
-        <v>-7.3</v>
-      </c>
-      <c r="G37" s="15">
-        <v>-18.14</v>
+        <v>27.35</v>
+      </c>
+      <c r="F37" s="7">
+        <v>-3.7</v>
+      </c>
+      <c r="G37" s="7">
+        <v>-11.23</v>
       </c>
       <c r="H37" s="8">
         <v>0</v>
@@ -3174,31 +3174,31 @@
     </row>
     <row r="38" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B38" s="11">
-        <v>11</v>
+        <v>40.25</v>
       </c>
       <c r="C38" s="11">
-        <v>40.25</v>
+        <v>32.950000000000003</v>
       </c>
       <c r="D38" s="11">
-        <v>42.1</v>
+        <v>41.55</v>
       </c>
       <c r="E38" s="11">
-        <v>10.8</v>
-      </c>
-      <c r="F38" s="14">
-        <v>29.25</v>
-      </c>
-      <c r="G38" s="14">
-        <v>265.91000000000003</v>
+        <v>28.55</v>
+      </c>
+      <c r="F38" s="15">
+        <v>-7.3</v>
+      </c>
+      <c r="G38" s="15">
+        <v>-18.14</v>
       </c>
       <c r="H38" s="13">
         <v>0</v>
       </c>
-      <c r="I38" s="12">
-        <v>-100</v>
+      <c r="I38" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="J38" s="13" t="s">
         <v>17</v>
@@ -3212,8 +3212,8 @@
       <c r="M38" s="13">
         <v>0</v>
       </c>
-      <c r="N38" s="12">
-        <v>-100</v>
+      <c r="N38" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="O38" s="13" t="s">
         <v>17</v>
@@ -3227,31 +3227,31 @@
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B39" s="6">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="C39" s="6">
-        <v>11</v>
+        <v>40.25</v>
       </c>
       <c r="D39" s="6">
-        <v>11.85</v>
+        <v>42.1</v>
       </c>
       <c r="E39" s="6">
-        <v>10.35</v>
-      </c>
-      <c r="F39" s="7">
-        <v>0.4</v>
-      </c>
-      <c r="G39" s="7">
-        <v>3.77</v>
+        <v>10.8</v>
+      </c>
+      <c r="F39" s="14">
+        <v>29.25</v>
+      </c>
+      <c r="G39" s="14">
+        <v>265.91000000000003</v>
       </c>
       <c r="H39" s="8">
-        <v>0.22700000000000001</v>
+        <v>0</v>
       </c>
       <c r="I39" s="7">
-        <v>48.1</v>
+        <v>-100</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>17</v>
@@ -3263,10 +3263,10 @@
         <v>17</v>
       </c>
       <c r="M39" s="8">
-        <v>0.22700000000000001</v>
+        <v>0</v>
       </c>
       <c r="N39" s="7">
-        <v>48.1</v>
+        <v>-100</v>
       </c>
       <c r="O39" s="8" t="s">
         <v>17</v>
@@ -3280,81 +3280,81 @@
     </row>
     <row r="40" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B40" s="11">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="C40" s="11">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="D40" s="11">
-        <v>11.45</v>
+        <v>11.85</v>
       </c>
       <c r="E40" s="11">
-        <v>10.3</v>
+        <v>10.35</v>
       </c>
       <c r="F40" s="12">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G40" s="12">
-        <v>-5.36</v>
+        <v>3.77</v>
       </c>
       <c r="H40" s="13">
-        <v>0.154</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>17</v>
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="I40" s="12">
+        <v>48.1</v>
       </c>
       <c r="J40" s="13" t="s">
         <v>17</v>
       </c>
       <c r="K40" s="13">
-        <v>0.154</v>
-      </c>
-      <c r="L40" s="12">
-        <v>-30.4</v>
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="M40" s="13">
-        <v>0.154</v>
-      </c>
-      <c r="N40" s="13" t="s">
-        <v>17</v>
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="N40" s="12">
+        <v>48.1</v>
       </c>
       <c r="O40" s="13" t="s">
         <v>17</v>
       </c>
       <c r="P40" s="13">
-        <v>0.154</v>
-      </c>
-      <c r="Q40" s="12">
-        <v>-30.4</v>
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="Q40" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B41" s="6">
-        <v>11.05</v>
+        <v>11.2</v>
       </c>
       <c r="C41" s="6">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D41" s="6">
-        <v>12.1</v>
+        <v>11.45</v>
       </c>
       <c r="E41" s="6">
         <v>10.3</v>
       </c>
       <c r="F41" s="7">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="G41" s="7">
-        <v>1.36</v>
+        <v>-5.36</v>
       </c>
       <c r="H41" s="8">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>17</v>
@@ -3363,13 +3363,13 @@
         <v>17</v>
       </c>
       <c r="K41" s="8">
-        <v>0</v>
-      </c>
-      <c r="L41" s="15">
-        <v>-100</v>
+        <v>0.154</v>
+      </c>
+      <c r="L41" s="7">
+        <v>-30.4</v>
       </c>
       <c r="M41" s="8">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="N41" s="8" t="s">
         <v>17</v>
@@ -3378,33 +3378,33 @@
         <v>17</v>
       </c>
       <c r="P41" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="15">
-        <v>-100</v>
+        <v>0.154</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>-30.4</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B42" s="11">
-        <v>13.45</v>
+        <v>11.05</v>
       </c>
       <c r="C42" s="11">
-        <v>11.05</v>
+        <v>11.2</v>
       </c>
       <c r="D42" s="11">
-        <v>14.3</v>
+        <v>12.1</v>
       </c>
       <c r="E42" s="11">
-        <v>9.7100000000000009</v>
+        <v>10.3</v>
       </c>
       <c r="F42" s="12">
-        <v>-2.4</v>
+        <v>0.15</v>
       </c>
       <c r="G42" s="12">
-        <v>-17.84</v>
+        <v>1.36</v>
       </c>
       <c r="H42" s="13">
         <v>0</v>
@@ -3412,13 +3412,13 @@
       <c r="I42" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="12">
-        <v>-100</v>
+      <c r="J42" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="K42" s="13">
         <v>0</v>
       </c>
-      <c r="L42" s="12">
+      <c r="L42" s="15">
         <v>-100</v>
       </c>
       <c r="M42" s="13">
@@ -3427,66 +3427,119 @@
       <c r="N42" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O42" s="12">
-        <v>-100</v>
+      <c r="O42" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="P42" s="13">
         <v>0</v>
       </c>
-      <c r="Q42" s="12">
+      <c r="Q42" s="15">
         <v>-100</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
+        <v>44835</v>
+      </c>
+      <c r="B43" s="6">
+        <v>13.45</v>
+      </c>
+      <c r="C43" s="6">
+        <v>11.05</v>
+      </c>
+      <c r="D43" s="6">
+        <v>14.3</v>
+      </c>
+      <c r="E43" s="6">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="F43" s="7">
+        <v>-2.4</v>
+      </c>
+      <c r="G43" s="7">
+        <v>-17.84</v>
+      </c>
+      <c r="H43" s="8">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="7">
+        <v>-100</v>
+      </c>
+      <c r="K43" s="8">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7">
+        <v>-100</v>
+      </c>
+      <c r="M43" s="8">
+        <v>0</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43" s="7">
+        <v>-100</v>
+      </c>
+      <c r="P43" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="10">
         <v>44805</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B44" s="11">
         <v>10.199999999999999</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C44" s="11">
         <v>13.45</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D44" s="11">
         <v>14</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E44" s="11">
         <v>9.1999999999999993</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F44" s="12">
         <v>3.25</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G44" s="12">
         <v>31.86</v>
       </c>
-      <c r="H43" s="8">
-        <v>0</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="8">
-        <v>0</v>
-      </c>
-      <c r="L43" s="15">
-        <v>-100</v>
-      </c>
-      <c r="M43" s="8">
-        <v>0</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="P43" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="15">
+      <c r="H44" s="13">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="13">
+        <v>0</v>
+      </c>
+      <c r="L44" s="15">
+        <v>-100</v>
+      </c>
+      <c r="M44" s="13">
+        <v>0</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="O44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="P44" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="15">
         <v>-100</v>
       </c>
     </row>
